--- a/artfynd/A 19812-2025 artfynd.xlsx
+++ b/artfynd/A 19812-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149465</v>
+        <v>122031908</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>803617</v>
+        <v>803144</v>
       </c>
       <c r="R2" t="n">
-        <v>7352335</v>
+        <v>7352273</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149482</v>
+        <v>122031909</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>803403</v>
+        <v>803137</v>
       </c>
       <c r="R3" t="n">
-        <v>7352696</v>
+        <v>7352284</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,42 +887,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152313</v>
+        <v>122031910</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>167</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803697</v>
+        <v>803151</v>
       </c>
       <c r="R4" t="n">
-        <v>7352320</v>
+        <v>7352273</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,42 +993,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149484</v>
+        <v>122031911</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>167</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803272</v>
+        <v>803135</v>
       </c>
       <c r="R5" t="n">
-        <v>7352636</v>
+        <v>7352276</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122031484</v>
+        <v>121149482</v>
       </c>
       <c r="B6" t="n">
-        <v>92082</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803401</v>
+        <v>803403</v>
       </c>
       <c r="R6" t="n">
-        <v>7352261</v>
+        <v>7352696</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122031514</v>
+        <v>121149478</v>
       </c>
       <c r="B7" t="n">
-        <v>92110</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>803294</v>
+        <v>803829</v>
       </c>
       <c r="R7" t="n">
-        <v>7352155</v>
+        <v>7352418</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122031911</v>
+        <v>121149481</v>
       </c>
       <c r="B8" t="n">
-        <v>97240</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,26 +1322,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>167</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>803135</v>
+        <v>803552</v>
       </c>
       <c r="R8" t="n">
-        <v>7352276</v>
+        <v>7352292</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,42 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122031857</v>
+        <v>121149484</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>803021</v>
+        <v>803272</v>
       </c>
       <c r="R9" t="n">
-        <v>7352321</v>
+        <v>7352636</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,42 +1523,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122031914</v>
+        <v>122031484</v>
       </c>
       <c r="B10" t="n">
-        <v>105308</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>803013</v>
+        <v>803401</v>
       </c>
       <c r="R10" t="n">
-        <v>7352322</v>
+        <v>7352261</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,42 +1629,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122031853</v>
+        <v>121152676</v>
       </c>
       <c r="B11" t="n">
-        <v>98202</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>803606</v>
+        <v>803412</v>
       </c>
       <c r="R11" t="n">
-        <v>7352340</v>
+        <v>7352390</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1698,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1782,6 +1732,4764 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122031381</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>803253</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7352212</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120288291</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>803519</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7352580</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121149477</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>803801</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7352449</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104158130</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>803602</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7352337</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104158182</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>803827</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7352373</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112610369</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>803567</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7352406</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121149457</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>803297</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7352649</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121149458</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>803359</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7352594</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121149461</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>803424</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7352550</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121149462</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>803478</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7352547</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121149463</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>803517</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7352486</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121149465</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>803617</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7352335</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121149466</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>803727</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7352429</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121149470</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>803790</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7352360</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121149471</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>803775</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7352342</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121149474</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>803869</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7352411</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121149486</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>803437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7352541</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121152312</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>803354</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7352270</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121152313</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>803697</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7352320</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122031842</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>803592</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7352357</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122031846</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>803111</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7352258</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122031853</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>803606</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7352340</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122031854</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>803480</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7352376</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122031856</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>802973</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7352429</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122031857</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>803021</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7352321</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122031859</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>803356</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7352338</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122031869</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>803507</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7352360</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122031870</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>803365</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7352315</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122031872</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>803120</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7352466</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122031873</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>803155</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7352259</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122031874</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>803129</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7352343</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122031882</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>803110</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7352453</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122031883</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>803019</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7352450</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122031884</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>803132</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7352253</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122031886</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>803352</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7352338</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122031903</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>803594</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7352314</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122031905</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>803493</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7352372</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122031906</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>803476</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7352376</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121149459</v>
+      </c>
+      <c r="B50" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>803373</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7352583</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121149460</v>
+      </c>
+      <c r="B51" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>803399</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7352571</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121149464</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>803572</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7352456</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121152674</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>803390</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7352370</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122031912</v>
+      </c>
+      <c r="B54" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>803479</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7352376</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122031913</v>
+      </c>
+      <c r="B55" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>803458</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7352374</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122031914</v>
+      </c>
+      <c r="B56" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>803013</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7352322</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19812-2025 artfynd.xlsx
+++ b/artfynd/A 19812-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031911</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149482</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149478</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149484</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031484</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152676</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031381</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288291</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149477</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158130</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158182</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610369</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2462,6 +2547,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149457</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2568,6 +2658,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149458</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2674,6 +2769,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149461</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149462</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2886,6 +2991,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149463</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2992,6 +3102,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149465</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3098,6 +3213,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149466</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3204,6 +3324,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149470</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3310,6 +3435,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149471</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3416,6 +3546,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149474</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3522,6 +3657,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149486</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3628,6 +3768,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152312</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3734,6 +3879,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152313</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3840,6 +3990,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031842</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3946,6 +4101,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031846</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4052,6 +4212,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031853</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4158,6 +4323,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031854</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4264,6 +4434,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031856</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4370,6 +4545,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031857</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4476,6 +4656,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031859</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4582,6 +4767,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031869</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4688,6 +4878,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031870</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4794,6 +4989,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031872</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4900,6 +5100,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031873</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5006,6 +5211,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031874</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5112,6 +5322,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031882</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5218,6 +5433,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031883</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5324,6 +5544,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031884</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5430,6 +5655,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031886</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5536,6 +5766,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031903</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5642,6 +5877,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031905</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5748,6 +5988,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031906</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5854,6 +6099,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149459</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5960,6 +6210,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149460</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6066,6 +6321,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149464</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6172,6 +6432,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152674</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6278,6 +6543,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031912</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6384,6 +6654,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031913</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6490,8 +6765,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>